--- a/output/yearly_total_coral_cover_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_4_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249849685080653</v>
+        <v>1.286999018209352</v>
       </c>
       <c r="C3" t="n">
-        <v>4.613847909126486</v>
+        <v>4.684543561309299</v>
       </c>
       <c r="D3" t="n">
-        <v>6.181500882646863</v>
+        <v>6.020003385298264</v>
       </c>
       <c r="E3" t="n">
-        <v>12.045198476854</v>
+        <v>11.99154596481691</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.371805636294355</v>
+        <v>1.455803347637392</v>
       </c>
       <c r="C4" t="n">
-        <v>5.090407901345374</v>
+        <v>5.294414126713255</v>
       </c>
       <c r="D4" t="n">
-        <v>6.489169806283244</v>
+        <v>6.257606057076045</v>
       </c>
       <c r="E4" t="n">
-        <v>12.95138334392297</v>
+        <v>13.00782353142669</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.5366223026693</v>
+        <v>1.669413341319381</v>
       </c>
       <c r="C5" t="n">
-        <v>5.68296730150464</v>
+        <v>6.115858264868263</v>
       </c>
       <c r="D5" t="n">
-        <v>6.934226776016309</v>
+        <v>6.52789118590005</v>
       </c>
       <c r="E5" t="n">
-        <v>14.15381638019025</v>
+        <v>14.31316279208769</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.738981097495067</v>
+        <v>1.902106458277679</v>
       </c>
       <c r="C6" t="n">
-        <v>6.467870472140209</v>
+        <v>7.121229048721702</v>
       </c>
       <c r="D6" t="n">
-        <v>7.342842447737574</v>
+        <v>6.898937400715837</v>
       </c>
       <c r="E6" t="n">
-        <v>15.54969401737285</v>
+        <v>15.92227290771522</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.969938682140666</v>
+        <v>2.167083514851029</v>
       </c>
       <c r="C7" t="n">
-        <v>7.397269790243937</v>
+        <v>8.286254988659424</v>
       </c>
       <c r="D7" t="n">
-        <v>7.744890831980972</v>
+        <v>7.209880900973832</v>
       </c>
       <c r="E7" t="n">
-        <v>17.11209930436558</v>
+        <v>17.66321940448429</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.212744881065415</v>
+        <v>1.349527722692828</v>
       </c>
       <c r="C8" t="n">
-        <v>5.147776441169046</v>
+        <v>5.87409518608228</v>
       </c>
       <c r="D8" t="n">
-        <v>6.03696776418736</v>
+        <v>5.466962505848353</v>
       </c>
       <c r="E8" t="n">
-        <v>12.39748908642182</v>
+        <v>12.69058541462346</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.516159624364115</v>
+        <v>1.675455357058858</v>
       </c>
       <c r="C9" t="n">
-        <v>6.407409648389877</v>
+        <v>7.245001013059942</v>
       </c>
       <c r="D9" t="n">
-        <v>6.651795376937531</v>
+        <v>5.878311188953119</v>
       </c>
       <c r="E9" t="n">
-        <v>14.57536464969152</v>
+        <v>14.79876755907192</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.817360308042592</v>
+        <v>2.019645345890018</v>
       </c>
       <c r="C10" t="n">
-        <v>7.8641033077131</v>
+        <v>8.777544476525794</v>
       </c>
       <c r="D10" t="n">
-        <v>7.22860909039887</v>
+        <v>6.375865603377192</v>
       </c>
       <c r="E10" t="n">
-        <v>16.91007270615456</v>
+        <v>17.173055425793</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.114764994114278</v>
+        <v>2.358829546639988</v>
       </c>
       <c r="C11" t="n">
-        <v>9.422685561508002</v>
+        <v>10.41538747280924</v>
       </c>
       <c r="D11" t="n">
-        <v>7.778683484409061</v>
+        <v>6.797566171942922</v>
       </c>
       <c r="E11" t="n">
-        <v>19.31613404003134</v>
+        <v>19.57178319139215</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.399318434681307</v>
+        <v>2.696728997816441</v>
       </c>
       <c r="C12" t="n">
-        <v>11.07496229373012</v>
+        <v>12.10552559214235</v>
       </c>
       <c r="D12" t="n">
-        <v>8.309428040565608</v>
+        <v>7.223700885404688</v>
       </c>
       <c r="E12" t="n">
-        <v>21.78370876897704</v>
+        <v>22.02595547536347</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.666452979153907</v>
+        <v>3.004183629275197</v>
       </c>
       <c r="C13" t="n">
-        <v>12.83028286576939</v>
+        <v>13.79854770814812</v>
       </c>
       <c r="D13" t="n">
-        <v>8.796767087433073</v>
+        <v>7.666853547640515</v>
       </c>
       <c r="E13" t="n">
-        <v>24.29350293235637</v>
+        <v>24.46958488506383</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536729681457532</v>
+        <v>1.730163431625281</v>
       </c>
       <c r="C14" t="n">
-        <v>8.94963170686801</v>
+        <v>9.658993510571539</v>
       </c>
       <c r="D14" t="n">
-        <v>6.63618251171857</v>
+        <v>5.846935897320474</v>
       </c>
       <c r="E14" t="n">
-        <v>17.12254390004411</v>
+        <v>17.23609283951729</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.541923126812998</v>
+        <v>1.756906239088964</v>
       </c>
       <c r="C15" t="n">
-        <v>9.844494739288976</v>
+        <v>10.3594606800746</v>
       </c>
       <c r="D15" t="n">
-        <v>6.667451176098831</v>
+        <v>5.823462309711932</v>
       </c>
       <c r="E15" t="n">
-        <v>18.05386904220081</v>
+        <v>17.9398292288755</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.758928639359713</v>
+        <v>2.022468993087727</v>
       </c>
       <c r="C16" t="n">
-        <v>11.79457947414259</v>
+        <v>12.1187329311308</v>
       </c>
       <c r="D16" t="n">
-        <v>7.162301106424436</v>
+        <v>6.238692501223121</v>
       </c>
       <c r="E16" t="n">
-        <v>20.71580921992673</v>
+        <v>20.37989442544165</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.38747457798089</v>
+        <v>1.611293419595078</v>
       </c>
       <c r="C17" t="n">
-        <v>11.04706695465202</v>
+        <v>10.98678764561127</v>
       </c>
       <c r="D17" t="n">
-        <v>6.661904301569836</v>
+        <v>5.768582613044535</v>
       </c>
       <c r="E17" t="n">
-        <v>19.09644583420275</v>
+        <v>18.36666367825088</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.55589339664443</v>
+        <v>1.8320688433261</v>
       </c>
       <c r="C18" t="n">
-        <v>12.98091358247739</v>
+        <v>12.69652090751117</v>
       </c>
       <c r="D18" t="n">
-        <v>7.127282165813951</v>
+        <v>6.160810455845222</v>
       </c>
       <c r="E18" t="n">
-        <v>21.66408914493577</v>
+        <v>20.6894002066825</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.536071910495687</v>
+        <v>1.834896276714332</v>
       </c>
       <c r="C19" t="n">
-        <v>13.96056034663711</v>
+        <v>13.43887925155444</v>
       </c>
       <c r="D19" t="n">
-        <v>7.224033402067474</v>
+        <v>6.23295909463032</v>
       </c>
       <c r="E19" t="n">
-        <v>22.72066565920028</v>
+        <v>21.50673462289909</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.68441398860738</v>
+        <v>2.039855744929937</v>
       </c>
       <c r="C20" t="n">
-        <v>15.9889394609044</v>
+        <v>15.30742983957035</v>
       </c>
       <c r="D20" t="n">
-        <v>7.664818486320208</v>
+        <v>6.607672558387242</v>
       </c>
       <c r="E20" t="n">
-        <v>25.33817193583199</v>
+        <v>23.95495814288753</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9931163426619886</v>
+        <v>1.212006810800857</v>
       </c>
       <c r="C21" t="n">
-        <v>11.67455099982137</v>
+        <v>11.11753680486286</v>
       </c>
       <c r="D21" t="n">
-        <v>6.386003744245356</v>
+        <v>5.505925832250345</v>
       </c>
       <c r="E21" t="n">
-        <v>19.05367108672872</v>
+        <v>17.83546944791406</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_4_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.286999018209352</v>
+        <v>1.268463621553173</v>
       </c>
       <c r="C3" t="n">
-        <v>4.684543561309299</v>
+        <v>4.596529879623573</v>
       </c>
       <c r="D3" t="n">
-        <v>6.020003385298264</v>
+        <v>6.081863308142854</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99154596481691</v>
+        <v>11.9468568093196</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.455803347637392</v>
+        <v>1.412241059734914</v>
       </c>
       <c r="C4" t="n">
-        <v>5.294414126713255</v>
+        <v>5.078695615743142</v>
       </c>
       <c r="D4" t="n">
-        <v>6.257606057076045</v>
+        <v>6.449401191543819</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00782353142669</v>
+        <v>12.94033786702187</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.669413341319381</v>
+        <v>1.61013736288331</v>
       </c>
       <c r="C5" t="n">
-        <v>6.115858264868263</v>
+        <v>5.681771300099578</v>
       </c>
       <c r="D5" t="n">
-        <v>6.52789118590005</v>
+        <v>6.800654694339455</v>
       </c>
       <c r="E5" t="n">
-        <v>14.31316279208769</v>
+        <v>14.09256335732234</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.902106458277679</v>
+        <v>1.844112279487595</v>
       </c>
       <c r="C6" t="n">
-        <v>7.121229048721702</v>
+        <v>6.479796772794605</v>
       </c>
       <c r="D6" t="n">
-        <v>6.898937400715837</v>
+        <v>7.24066110176575</v>
       </c>
       <c r="E6" t="n">
-        <v>15.92227290771522</v>
+        <v>15.56457015404795</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.167083514851029</v>
+        <v>2.105405411600879</v>
       </c>
       <c r="C7" t="n">
-        <v>8.286254988659424</v>
+        <v>7.442273246431448</v>
       </c>
       <c r="D7" t="n">
-        <v>7.209880900973832</v>
+        <v>7.680892426217202</v>
       </c>
       <c r="E7" t="n">
-        <v>17.66321940448429</v>
+        <v>17.22857108424953</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.349527722692828</v>
+        <v>1.327712316933228</v>
       </c>
       <c r="C8" t="n">
-        <v>5.87409518608228</v>
+        <v>5.182193245235848</v>
       </c>
       <c r="D8" t="n">
-        <v>5.466962505848353</v>
+        <v>5.923912685879117</v>
       </c>
       <c r="E8" t="n">
-        <v>12.69058541462346</v>
+        <v>12.43381824804819</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.675455357058858</v>
+        <v>1.688340166901575</v>
       </c>
       <c r="C9" t="n">
-        <v>7.245001013059942</v>
+        <v>6.398937203432618</v>
       </c>
       <c r="D9" t="n">
-        <v>5.878311188953119</v>
+        <v>6.466982594238059</v>
       </c>
       <c r="E9" t="n">
-        <v>14.79876755907192</v>
+        <v>14.55425996457225</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.019645345890018</v>
+        <v>2.063468273747894</v>
       </c>
       <c r="C10" t="n">
-        <v>8.777544476525794</v>
+        <v>7.762190333383578</v>
       </c>
       <c r="D10" t="n">
-        <v>6.375865603377192</v>
+        <v>7.019539119106592</v>
       </c>
       <c r="E10" t="n">
-        <v>17.173055425793</v>
+        <v>16.84519772623807</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.358829546639988</v>
+        <v>2.430209252574605</v>
       </c>
       <c r="C11" t="n">
-        <v>10.41538747280924</v>
+        <v>9.236536347174427</v>
       </c>
       <c r="D11" t="n">
-        <v>6.797566171942922</v>
+        <v>7.594899217782843</v>
       </c>
       <c r="E11" t="n">
-        <v>19.57178319139215</v>
+        <v>19.26164481753187</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.696728997816441</v>
+        <v>2.789723428731335</v>
       </c>
       <c r="C12" t="n">
-        <v>12.10552559214235</v>
+        <v>10.74848457927724</v>
       </c>
       <c r="D12" t="n">
-        <v>7.223700885404688</v>
+        <v>8.109441045144768</v>
       </c>
       <c r="E12" t="n">
-        <v>22.02595547536347</v>
+        <v>21.64764905315334</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.004183629275197</v>
+        <v>3.136900172486925</v>
       </c>
       <c r="C13" t="n">
-        <v>13.79854770814812</v>
+        <v>12.26517901190109</v>
       </c>
       <c r="D13" t="n">
-        <v>7.666853547640515</v>
+        <v>8.675069121944851</v>
       </c>
       <c r="E13" t="n">
-        <v>24.46958488506383</v>
+        <v>24.07714830633287</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.730163431625281</v>
+        <v>1.797128442531956</v>
       </c>
       <c r="C14" t="n">
-        <v>9.658993510571539</v>
+        <v>8.540606160847659</v>
       </c>
       <c r="D14" t="n">
-        <v>5.846935897320474</v>
+        <v>6.559939985006762</v>
       </c>
       <c r="E14" t="n">
-        <v>17.23609283951729</v>
+        <v>16.89767458838638</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.756906239088964</v>
+        <v>1.842102304863503</v>
       </c>
       <c r="C15" t="n">
-        <v>10.3594606800746</v>
+        <v>9.190640950783557</v>
       </c>
       <c r="D15" t="n">
-        <v>5.823462309711932</v>
+        <v>6.622565671060666</v>
       </c>
       <c r="E15" t="n">
-        <v>17.9398292288755</v>
+        <v>17.65530892670773</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.022468993087727</v>
+        <v>2.140985575944402</v>
       </c>
       <c r="C16" t="n">
-        <v>12.1187329311308</v>
+        <v>10.80932693059161</v>
       </c>
       <c r="D16" t="n">
-        <v>6.238692501223121</v>
+        <v>7.192813825072427</v>
       </c>
       <c r="E16" t="n">
-        <v>20.37989442544165</v>
+        <v>20.14312633160844</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.611293419595078</v>
+        <v>1.720129970087879</v>
       </c>
       <c r="C17" t="n">
-        <v>10.98678764561127</v>
+        <v>9.92386904117733</v>
       </c>
       <c r="D17" t="n">
-        <v>5.768582613044535</v>
+        <v>6.722684301939757</v>
       </c>
       <c r="E17" t="n">
-        <v>18.36666367825088</v>
+        <v>18.36668331320497</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.8320688433261</v>
+        <v>1.971015595908152</v>
       </c>
       <c r="C18" t="n">
-        <v>12.69652090751117</v>
+        <v>11.57135949862799</v>
       </c>
       <c r="D18" t="n">
-        <v>6.160810455845222</v>
+        <v>7.232319352691318</v>
       </c>
       <c r="E18" t="n">
-        <v>20.6894002066825</v>
+        <v>20.77469444722746</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.834896276714332</v>
+        <v>1.98306164023926</v>
       </c>
       <c r="C19" t="n">
-        <v>13.43887925155444</v>
+        <v>12.38504181338479</v>
       </c>
       <c r="D19" t="n">
-        <v>6.23295909463032</v>
+        <v>7.365797770560714</v>
       </c>
       <c r="E19" t="n">
-        <v>21.50673462289909</v>
+        <v>21.73390122418476</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.039855744929937</v>
+        <v>2.212034657300743</v>
       </c>
       <c r="C20" t="n">
-        <v>15.30742983957035</v>
+        <v>14.21257498231727</v>
       </c>
       <c r="D20" t="n">
-        <v>6.607672558387242</v>
+        <v>7.875128479523959</v>
       </c>
       <c r="E20" t="n">
-        <v>23.95495814288753</v>
+        <v>24.29973811914197</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.212006810800857</v>
+        <v>1.318231912400362</v>
       </c>
       <c r="C21" t="n">
-        <v>11.11753680486286</v>
+        <v>10.46072795576766</v>
       </c>
       <c r="D21" t="n">
-        <v>5.505925832250345</v>
+        <v>6.606543548527359</v>
       </c>
       <c r="E21" t="n">
-        <v>17.83546944791406</v>
+        <v>18.38550341669538</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_4_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.268463621553173</v>
+        <v>2.584509258175513</v>
       </c>
       <c r="C3" t="n">
-        <v>4.596529879623573</v>
+        <v>7.676596628127675</v>
       </c>
       <c r="D3" t="n">
-        <v>6.081863308142854</v>
+        <v>8.165438898204206</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9468568093196</v>
+        <v>18.42654478450739</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.412241059734914</v>
+        <v>1.050713592354701</v>
       </c>
       <c r="C4" t="n">
-        <v>5.078695615743142</v>
+        <v>4.43124732446755</v>
       </c>
       <c r="D4" t="n">
-        <v>6.449401191543819</v>
+        <v>5.766168042316195</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94033786702187</v>
+        <v>11.24812895913845</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.61013736288331</v>
+        <v>1.119545903080519</v>
       </c>
       <c r="C5" t="n">
-        <v>5.681771300099578</v>
+        <v>5.013956380515822</v>
       </c>
       <c r="D5" t="n">
-        <v>6.800654694339455</v>
+        <v>6.051134810528217</v>
       </c>
       <c r="E5" t="n">
-        <v>14.09256335732234</v>
+        <v>12.18463709412456</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.844112279487595</v>
+        <v>1.194250246891161</v>
       </c>
       <c r="C6" t="n">
-        <v>6.479796772794605</v>
+        <v>5.745018002547718</v>
       </c>
       <c r="D6" t="n">
-        <v>7.24066110176575</v>
+        <v>6.405024011778983</v>
       </c>
       <c r="E6" t="n">
-        <v>15.56457015404795</v>
+        <v>13.34429226121786</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.105405411600879</v>
+        <v>1.280710736934831</v>
       </c>
       <c r="C7" t="n">
-        <v>7.442273246431448</v>
+        <v>6.641249845934024</v>
       </c>
       <c r="D7" t="n">
-        <v>7.680892426217202</v>
+        <v>6.780485730310375</v>
       </c>
       <c r="E7" t="n">
-        <v>17.22857108424953</v>
+        <v>14.70244631317923</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.327712316933228</v>
+        <v>1.373301837846479</v>
       </c>
       <c r="C8" t="n">
-        <v>5.182193245235848</v>
+        <v>7.673983631474774</v>
       </c>
       <c r="D8" t="n">
-        <v>5.923912685879117</v>
+        <v>7.201446765940744</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43381824804819</v>
+        <v>16.248732235262</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.688340166901575</v>
+        <v>1.469800821368</v>
       </c>
       <c r="C9" t="n">
-        <v>6.398937203432618</v>
+        <v>8.83144000412036</v>
       </c>
       <c r="D9" t="n">
-        <v>6.466982594238059</v>
+        <v>7.635523646153338</v>
       </c>
       <c r="E9" t="n">
-        <v>14.55425996457225</v>
+        <v>17.9367644716417</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.063468273747894</v>
+        <v>0.9457273809779948</v>
       </c>
       <c r="C10" t="n">
-        <v>7.762190333383578</v>
+        <v>6.569286223151192</v>
       </c>
       <c r="D10" t="n">
-        <v>7.019539119106592</v>
+        <v>6.028245063340774</v>
       </c>
       <c r="E10" t="n">
-        <v>16.84519772623807</v>
+        <v>13.54325866746996</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.430209252574605</v>
+        <v>0.8636925428111314</v>
       </c>
       <c r="C11" t="n">
-        <v>9.236536347174427</v>
+        <v>6.933946590416628</v>
       </c>
       <c r="D11" t="n">
-        <v>7.594899217782843</v>
+        <v>5.914303424785889</v>
       </c>
       <c r="E11" t="n">
-        <v>19.26164481753187</v>
+        <v>13.71194255801365</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.789723428731335</v>
+        <v>0.9071937835863076</v>
       </c>
       <c r="C12" t="n">
-        <v>10.74848457927724</v>
+        <v>8.14732784800343</v>
       </c>
       <c r="D12" t="n">
-        <v>8.109441045144768</v>
+        <v>6.331094595146831</v>
       </c>
       <c r="E12" t="n">
-        <v>21.64764905315334</v>
+        <v>15.38561622673657</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.136900172486925</v>
+        <v>0.7033829601846698</v>
       </c>
       <c r="C13" t="n">
-        <v>12.26517901190109</v>
+        <v>7.714897436713838</v>
       </c>
       <c r="D13" t="n">
-        <v>8.675069121944851</v>
+        <v>5.799478213297183</v>
       </c>
       <c r="E13" t="n">
-        <v>24.07714830633287</v>
+        <v>14.21775861019569</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.797128442531956</v>
+        <v>0.7491814905877835</v>
       </c>
       <c r="C14" t="n">
-        <v>8.540606160847659</v>
+        <v>9.053314081913514</v>
       </c>
       <c r="D14" t="n">
-        <v>6.559939985006762</v>
+        <v>6.239703701358495</v>
       </c>
       <c r="E14" t="n">
-        <v>16.89767458838638</v>
+        <v>16.04219927385979</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.842102304863503</v>
+        <v>0.7159787832301564</v>
       </c>
       <c r="C15" t="n">
-        <v>9.190640950783557</v>
+        <v>9.808464598543118</v>
       </c>
       <c r="D15" t="n">
-        <v>6.622565671060666</v>
+        <v>6.338408615543469</v>
       </c>
       <c r="E15" t="n">
-        <v>17.65530892670773</v>
+        <v>16.86285199731674</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.140985575944402</v>
+        <v>0.7753548843830035</v>
       </c>
       <c r="C16" t="n">
-        <v>10.80932693059161</v>
+        <v>11.52346984561483</v>
       </c>
       <c r="D16" t="n">
-        <v>7.192813825072427</v>
+        <v>6.816676827144346</v>
       </c>
       <c r="E16" t="n">
-        <v>20.14312633160844</v>
+        <v>19.11550155714218</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.720129970087879</v>
+        <v>0.4705909445536661</v>
       </c>
       <c r="C17" t="n">
-        <v>9.92386904117733</v>
+        <v>8.71618192027516</v>
       </c>
       <c r="D17" t="n">
-        <v>6.722684301939757</v>
+        <v>5.70447448795722</v>
       </c>
       <c r="E17" t="n">
-        <v>18.36668331320497</v>
+        <v>14.89124735278605</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.971015595908152</v>
+        <v>0.3547250804984576</v>
       </c>
       <c r="C18" t="n">
-        <v>11.57135949862799</v>
+        <v>7.780016761936528</v>
       </c>
       <c r="D18" t="n">
-        <v>7.232319352691318</v>
+        <v>5.229220241808381</v>
       </c>
       <c r="E18" t="n">
-        <v>20.77469444722746</v>
+        <v>13.36396208424337</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.98306164023926</v>
+        <v>0.4140520942660924</v>
       </c>
       <c r="C19" t="n">
-        <v>12.38504181338479</v>
+        <v>9.644316382393052</v>
       </c>
       <c r="D19" t="n">
-        <v>7.365797770560714</v>
+        <v>5.774610543948612</v>
       </c>
       <c r="E19" t="n">
-        <v>21.73390122418476</v>
+        <v>15.83297902060776</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.212034657300743</v>
+        <v>0.4655545788308799</v>
       </c>
       <c r="C20" t="n">
-        <v>14.21257498231727</v>
+        <v>11.62118319461851</v>
       </c>
       <c r="D20" t="n">
-        <v>7.875128479523959</v>
+        <v>6.369863811987537</v>
       </c>
       <c r="E20" t="n">
-        <v>24.29973811914197</v>
+        <v>18.45660158543693</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.318231912400362</v>
+        <v>0.5145437892727958</v>
       </c>
       <c r="C21" t="n">
-        <v>10.46072795576766</v>
+        <v>13.6530278782818</v>
       </c>
       <c r="D21" t="n">
-        <v>6.606543548527359</v>
+        <v>6.898407323522892</v>
       </c>
       <c r="E21" t="n">
-        <v>18.38550341669538</v>
+        <v>21.06597899107749</v>
       </c>
     </row>
   </sheetData>
